--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CeePeez\Desktop\karspa_whatsapp_backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA739C6-2B25-4C5F-B23E-9D6A37D90687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C3ABB4-3AD4-4836-B41E-E616DF46BC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vehicle_Database" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="951">
   <si>
     <t>Booking_ID</t>
   </si>
@@ -2779,12 +2779,6 @@
     <t>volvo xc90, volvo xc90 car, volvo xc90 model, volvoxc90, xc90, xc90 car, xc90 model</t>
   </si>
   <si>
-    <t>Signature Essential Detail</t>
-  </si>
-  <si>
-    <t>Signature Deep Detail + Engine Care</t>
-  </si>
-  <si>
     <t>Paint Enhancement</t>
   </si>
   <si>
@@ -2795,9 +2789,6 @@
   </si>
   <si>
     <t>Borophene Coating</t>
-  </si>
-  <si>
-    <t>PPF (Paint Protection Film)</t>
   </si>
   <si>
     <t>Vinyl Wrap &amp; Styling</t>
@@ -2911,6 +2902,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="[$-14009]hh:mm;@"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2961,7 +2955,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2969,6 +2963,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10419,34 +10414,34 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="C1" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>923</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>953</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -10846,72 +10841,72 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>928</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>929</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>930</v>
-      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>918</v>
+      <c r="A2" s="1" t="s">
+        <v>948</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="D2" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>919</v>
+        <v>949</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="D3" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="D4" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B5">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="D5" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -10922,80 +10917,80 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D6" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B7">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="D7" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B8">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="D8" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>924</v>
+        <v>950</v>
       </c>
       <c r="B9">
         <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="D9" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="B10">
         <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="D10" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="D11" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
     </row>
   </sheetData>
@@ -11007,6 +11002,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="9" max="9" width="8.7265625" style="3"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -11033,7 +11031,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -11068,7 +11066,7 @@
       <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J2" t="s">
@@ -11097,7 +11095,7 @@
       <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J3" t="s">
